--- a/filtered_dataset_binary_classification_analysis.xlsx
+++ b/filtered_dataset_binary_classification_analysis.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Владелец\.vscode\oncotagger\45к\wos_oncoarticleclassifier\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E18A280E-6310-4C91-B716-4B8977F1A182}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{39D44D8F-EC8B-4661-B2C2-0D36D08338A6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3675" yWindow="3675" windowWidth="21600" windowHeight="11295" tabRatio="671" firstSheet="4" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Cancer Type Distribution" sheetId="7" r:id="rId1"/>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="151" uniqueCount="61">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="157" uniqueCount="63">
   <si>
     <t>breast cancer</t>
   </si>
@@ -214,23 +214,29 @@
     <t>Publication Year</t>
   </si>
   <si>
-    <t>how_many_cancer_studied</t>
-  </si>
-  <si>
-    <t>not specified</t>
-  </si>
-  <si>
     <t>cancer type</t>
   </si>
   <si>
     <t>AI model</t>
+  </si>
+  <si>
+    <t>%</t>
+  </si>
+  <si>
+    <t>Cancer Type</t>
+  </si>
+  <si>
+    <t>% from all</t>
+  </si>
+  <si>
+    <t>% from categorized</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -246,13 +252,28 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="204"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0" tint="-0.14999847407452621"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="2">
@@ -282,7 +303,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
@@ -301,6 +322,22 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="10" fontId="2" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="10" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -640,274 +677,518 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
-  <dimension ref="A1:B33"/>
+  <dimension ref="A1:D41"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="44.5703125" customWidth="1"/>
+    <col min="3" max="3" width="9.140625" style="7"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="B1" s="1" t="s">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1" s="8" t="s">
+        <v>60</v>
+      </c>
+      <c r="B1" s="8" t="s">
         <v>48</v>
       </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C1" s="9" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
-        <v>58</v>
+        <v>0</v>
       </c>
       <c r="B2">
-        <v>6526</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+        <v>3434</v>
+      </c>
+      <c r="C2" s="7">
+        <f>B2/D7</f>
+        <v>0.17480274879104099</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="B3">
-        <v>3434</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+        <v>2436</v>
+      </c>
+      <c r="C3" s="7">
+        <f t="shared" ref="C3:C32" si="0">B3/D8</f>
+        <v>0.12400101807075592</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B4">
-        <v>2436</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+        <v>2190</v>
+      </c>
+      <c r="C4" s="7">
+        <f t="shared" si="0"/>
+        <v>0.11147874777297022</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="B5">
+        <v>2033</v>
+      </c>
+      <c r="C5" s="7">
+        <f t="shared" si="0"/>
+        <v>0.10348689233901756</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A6" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="B6">
+        <v>1422</v>
+      </c>
+      <c r="C6" s="7">
+        <f t="shared" si="0"/>
+        <v>7.2384830745736831E-2</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A7" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B7">
+        <v>1043</v>
+      </c>
+      <c r="C7" s="7">
+        <f t="shared" si="0"/>
+        <v>5.309238992109952E-2</v>
+      </c>
+      <c r="D7">
+        <f>SUM(B2:B32)</f>
+        <v>19645</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A8" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B8">
+        <v>1032</v>
+      </c>
+      <c r="C8" s="7">
+        <f t="shared" si="0"/>
+        <v>5.2532451005344871E-2</v>
+      </c>
+      <c r="D8">
+        <v>19645</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A9" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="B9">
+        <v>986</v>
+      </c>
+      <c r="C9" s="7">
+        <f t="shared" si="0"/>
+        <v>5.019088826673454E-2</v>
+      </c>
+      <c r="D9">
+        <v>19645</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A10" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="B10">
+        <v>627</v>
+      </c>
+      <c r="C10" s="7">
+        <f t="shared" si="0"/>
+        <v>3.1916518198014762E-2</v>
+      </c>
+      <c r="D10">
+        <v>19645</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A11" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B11">
+        <v>594</v>
+      </c>
+      <c r="C11" s="7">
+        <f t="shared" si="0"/>
+        <v>3.0236701450750827E-2</v>
+      </c>
+      <c r="D11">
+        <v>19645</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A12" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="B12">
+        <v>528</v>
+      </c>
+      <c r="C12" s="7">
+        <f t="shared" si="0"/>
+        <v>2.6877067956222956E-2</v>
+      </c>
+      <c r="D12">
+        <v>19645</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A13" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B13">
+        <v>458</v>
+      </c>
+      <c r="C13" s="7">
+        <f t="shared" si="0"/>
+        <v>2.3313820310511581E-2</v>
+      </c>
+      <c r="D13">
+        <v>19645</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A14" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B14">
+        <v>403</v>
+      </c>
+      <c r="C14" s="7">
+        <f t="shared" si="0"/>
+        <v>2.0514125731738355E-2</v>
+      </c>
+      <c r="D14">
+        <v>19645</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A15" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="B15">
+        <v>368</v>
+      </c>
+      <c r="C15" s="7">
+        <f t="shared" si="0"/>
+        <v>1.8732501908882666E-2</v>
+      </c>
+      <c r="D15">
+        <v>19645</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A16" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B16">
+        <v>319</v>
+      </c>
+      <c r="C16" s="7">
+        <f t="shared" si="0"/>
+        <v>1.6238228556884702E-2</v>
+      </c>
+      <c r="D16">
+        <v>19645</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A17" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="B17">
+        <v>315</v>
+      </c>
+      <c r="C17" s="7">
+        <f t="shared" si="0"/>
+        <v>1.6034614405701197E-2</v>
+      </c>
+      <c r="D17">
+        <v>19645</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A18" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="B18">
+        <v>281</v>
+      </c>
+      <c r="C18" s="7">
+        <f t="shared" si="0"/>
+        <v>1.4303894120641385E-2</v>
+      </c>
+      <c r="D18">
+        <v>19645</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A19" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B19">
+        <v>275</v>
+      </c>
+      <c r="C19" s="7">
+        <f t="shared" si="0"/>
+        <v>1.3998472893866123E-2</v>
+      </c>
+      <c r="D19">
+        <v>19645</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A20" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="B20">
+        <v>238</v>
+      </c>
+      <c r="C20" s="7">
+        <f t="shared" si="0"/>
+        <v>1.2115041995418682E-2</v>
+      </c>
+      <c r="D20">
+        <v>19645</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A21" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="B21">
+        <v>205</v>
+      </c>
+      <c r="C21" s="7">
+        <f t="shared" si="0"/>
+        <v>1.0435225248154746E-2</v>
+      </c>
+      <c r="D21">
+        <v>19645</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A22" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="B22">
+        <v>188</v>
+      </c>
+      <c r="C22" s="7">
+        <f t="shared" si="0"/>
+        <v>9.5698651056248408E-3</v>
+      </c>
+      <c r="D22">
+        <v>19645</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A23" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B23">
+        <v>114</v>
+      </c>
+      <c r="C23" s="7">
+        <f t="shared" si="0"/>
+        <v>5.8030033087299567E-3</v>
+      </c>
+      <c r="D23">
+        <v>19645</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A24" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B24">
+        <v>40</v>
+      </c>
+      <c r="C24" s="7">
+        <f t="shared" si="0"/>
+        <v>2.0361415118350726E-3</v>
+      </c>
+      <c r="D24">
+        <v>19645</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A25" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B25">
+        <v>35</v>
+      </c>
+      <c r="C25" s="7">
+        <f t="shared" si="0"/>
+        <v>1.7816238228556885E-3</v>
+      </c>
+      <c r="D25">
+        <v>19645</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A26" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="B26">
+        <v>32</v>
+      </c>
+      <c r="C26" s="7">
+        <f t="shared" si="0"/>
+        <v>1.628913209468058E-3</v>
+      </c>
+      <c r="D26">
+        <v>19645</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A27" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B27">
+        <v>16</v>
+      </c>
+      <c r="C27" s="7">
+        <f t="shared" si="0"/>
+        <v>8.1445660473402899E-4</v>
+      </c>
+      <c r="D27">
+        <v>19645</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A28" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="B28">
+        <v>14</v>
+      </c>
+      <c r="C28" s="7">
+        <f t="shared" si="0"/>
+        <v>7.1264952914227534E-4</v>
+      </c>
+      <c r="D28">
+        <v>19645</v>
+      </c>
+    </row>
+    <row r="29" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A29" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="B29">
+        <v>9</v>
+      </c>
+      <c r="C29" s="7">
+        <f t="shared" si="0"/>
+        <v>4.5813184016289132E-4</v>
+      </c>
+      <c r="D29">
+        <v>19645</v>
+      </c>
+    </row>
+    <row r="30" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A30" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B30">
+        <v>6</v>
+      </c>
+      <c r="C30" s="7">
+        <f t="shared" si="0"/>
+        <v>3.054212267752609E-4</v>
+      </c>
+      <c r="D30">
+        <v>19645</v>
+      </c>
+    </row>
+    <row r="31" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A31" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="B31">
         <v>3</v>
       </c>
-      <c r="B5">
-        <v>2190</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A6" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="B6">
-        <v>2033</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A7" s="1" t="s">
+      <c r="C31" s="7">
+        <f t="shared" si="0"/>
+        <v>1.5271061338763045E-4</v>
+      </c>
+      <c r="D31">
+        <v>19645</v>
+      </c>
+    </row>
+    <row r="32" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A32" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="B32">
         <v>1</v>
       </c>
-      <c r="B7">
-        <v>1422</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A8" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="B8">
-        <v>1043</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A9" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="B9">
-        <v>1032</v>
-      </c>
-    </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A10" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="B10">
-        <v>986</v>
-      </c>
-    </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A11" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="B11">
-        <v>627</v>
-      </c>
-    </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A12" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B12">
-        <v>594</v>
-      </c>
-    </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A13" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="B13">
-        <v>528</v>
-      </c>
-    </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A14" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="B14">
-        <v>458</v>
-      </c>
-    </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A15" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="B15">
-        <v>403</v>
-      </c>
-    </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A16" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="B16">
-        <v>368</v>
-      </c>
-    </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A17" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="B17">
-        <v>319</v>
-      </c>
-    </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A18" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="B18">
-        <v>315</v>
-      </c>
-    </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A19" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="B19">
-        <v>281</v>
-      </c>
-    </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A20" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="B20">
-        <v>275</v>
-      </c>
-    </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A21" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="B21">
-        <v>238</v>
-      </c>
-    </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A22" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="B22">
-        <v>205</v>
-      </c>
-    </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A23" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="B23">
-        <v>188</v>
-      </c>
-    </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A24" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="B24">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A25" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="B25">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A26" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="B26">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A27" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="B27">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A28" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="B28">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A29" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="B29">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A30" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="B30">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A31" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="B31">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A32" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="B32">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A33" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="B33">
-        <v>1</v>
+      <c r="C32" s="7">
+        <f t="shared" si="0"/>
+        <v>5.0903537795876812E-5</v>
+      </c>
+      <c r="D32">
+        <v>19645</v>
+      </c>
+    </row>
+    <row r="33" spans="4:4" x14ac:dyDescent="0.25">
+      <c r="D33">
+        <v>19645</v>
+      </c>
+    </row>
+    <row r="34" spans="4:4" x14ac:dyDescent="0.25">
+      <c r="D34">
+        <v>19645</v>
+      </c>
+    </row>
+    <row r="35" spans="4:4" x14ac:dyDescent="0.25">
+      <c r="D35">
+        <v>19645</v>
+      </c>
+    </row>
+    <row r="36" spans="4:4" x14ac:dyDescent="0.25">
+      <c r="D36">
+        <v>19645</v>
+      </c>
+    </row>
+    <row r="37" spans="4:4" x14ac:dyDescent="0.25">
+      <c r="D37">
+        <v>19645</v>
+      </c>
+    </row>
+    <row r="38" spans="4:4" x14ac:dyDescent="0.25">
+      <c r="D38">
+        <v>19645</v>
+      </c>
+    </row>
+    <row r="39" spans="4:4" x14ac:dyDescent="0.25">
+      <c r="D39">
+        <v>19645</v>
+      </c>
+    </row>
+    <row r="40" spans="4:4" x14ac:dyDescent="0.25">
+      <c r="D40">
+        <v>19645</v>
+      </c>
+    </row>
+    <row r="41" spans="4:4" x14ac:dyDescent="0.25">
+      <c r="D41">
+        <v>19645</v>
       </c>
     </row>
   </sheetData>
@@ -925,7 +1206,7 @@
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>48</v>
@@ -937,6 +1218,10 @@
       </c>
       <c r="B2">
         <v>3778</v>
+      </c>
+      <c r="C2">
+        <f>B2/E16</f>
+        <v>0.17612232529951985</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
@@ -1203,146 +1488,220 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:B17"/>
+  <dimension ref="A1:C18"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="46.85546875" customWidth="1"/>
+    <col min="3" max="3" width="9.140625" style="7"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>48</v>
       </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C1" s="7" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>35</v>
       </c>
       <c r="B2">
         <v>5622</v>
       </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C2" s="7">
+        <f>B2/23198</f>
+        <v>0.2423484783170963</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>33</v>
       </c>
       <c r="B3">
         <v>3594</v>
       </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C3" s="7">
+        <f t="shared" ref="C3:C17" si="0">B3/23198</f>
+        <v>0.15492714889214587</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
         <v>32</v>
       </c>
       <c r="B4">
         <v>2662</v>
       </c>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C4" s="7">
+        <f t="shared" si="0"/>
+        <v>0.11475127166135012</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
         <v>45</v>
       </c>
       <c r="B5">
         <v>2547</v>
       </c>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C5" s="7">
+        <f t="shared" si="0"/>
+        <v>0.10979394775411673</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
         <v>38</v>
       </c>
       <c r="B6">
         <v>1889</v>
       </c>
-    </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C6" s="7">
+        <f t="shared" si="0"/>
+        <v>8.1429433571859638E-2</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
         <v>34</v>
       </c>
       <c r="B7">
         <v>1412</v>
       </c>
-    </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C7" s="7">
+        <f t="shared" si="0"/>
+        <v>6.0867316147943787E-2</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
         <v>47</v>
       </c>
       <c r="B8">
         <v>1375</v>
       </c>
-    </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C8" s="7">
+        <f t="shared" si="0"/>
+        <v>5.9272351064746959E-2</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
         <v>46</v>
       </c>
       <c r="B9">
         <v>1225</v>
       </c>
-    </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C9" s="7">
+        <f t="shared" si="0"/>
+        <v>5.2806276403138203E-2</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
         <v>36</v>
       </c>
       <c r="B10">
         <v>741</v>
       </c>
-    </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C10" s="7">
+        <f t="shared" si="0"/>
+        <v>3.1942408828347271E-2</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
         <v>37</v>
       </c>
       <c r="B11">
         <v>661</v>
       </c>
-    </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C11" s="7">
+        <f t="shared" si="0"/>
+        <v>2.8493835675489267E-2</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
         <v>44</v>
       </c>
       <c r="B12">
         <v>554</v>
       </c>
-    </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C12" s="7">
+        <f t="shared" si="0"/>
+        <v>2.3881369083541684E-2</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
         <v>43</v>
       </c>
       <c r="B13">
         <v>526</v>
       </c>
-    </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C13" s="7">
+        <f t="shared" si="0"/>
+        <v>2.2674368480041382E-2</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
         <v>39</v>
       </c>
       <c r="B14">
         <v>222</v>
       </c>
-    </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C14" s="7">
+        <f t="shared" si="0"/>
+        <v>9.5697904991809638E-3</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
         <v>40</v>
       </c>
       <c r="B15">
         <v>114</v>
       </c>
-    </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C15" s="7">
+        <f t="shared" si="0"/>
+        <v>4.9142167428226574E-3</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
         <v>41</v>
       </c>
       <c r="B16">
         <v>28</v>
       </c>
-    </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C16" s="7">
+        <f t="shared" si="0"/>
+        <v>1.2070006035003018E-3</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
         <v>42</v>
       </c>
       <c r="B17">
         <v>26</v>
+      </c>
+      <c r="C17" s="7">
+        <f t="shared" si="0"/>
+        <v>1.1207862746788516E-3</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B18">
+        <f>SUM(B2:B17)</f>
+        <v>23198</v>
       </c>
     </row>
   </sheetData>
@@ -1357,66 +1716,131 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:B7"/>
+  <dimension ref="A1:D9"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="46.7109375" customWidth="1"/>
+    <col min="3" max="3" width="11.85546875" style="7" customWidth="1"/>
+    <col min="4" max="4" width="19.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>49</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>48</v>
       </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C1" s="7" t="s">
+        <v>61</v>
+      </c>
+      <c r="D1" s="7" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="B2">
+        <v>6577</v>
+      </c>
+      <c r="C2" s="7">
+        <f>B2/26171</f>
+        <v>0.25130870046998588</v>
+      </c>
+      <c r="D2" s="7">
+        <f>B2/16290</f>
+        <v>0.40374462860650706</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A3" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="B3">
+        <v>4322</v>
+      </c>
+      <c r="C3" s="7">
+        <f t="shared" ref="C3:D7" si="0">B3/26171</f>
+        <v>0.16514462573077071</v>
+      </c>
+      <c r="D3" s="7">
+        <f t="shared" ref="D3:D7" si="1">B3/16290</f>
+        <v>0.26531614487415595</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A4" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="B4">
+        <v>3539</v>
+      </c>
+      <c r="C4" s="7">
+        <f t="shared" si="0"/>
+        <v>0.13522601352642238</v>
+      </c>
+      <c r="D4" s="7">
+        <f t="shared" si="1"/>
+        <v>0.2172498465316145</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A5" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="B5">
+        <v>1485</v>
+      </c>
+      <c r="C5" s="7">
+        <f t="shared" si="0"/>
+        <v>5.6742195559970961E-2</v>
+      </c>
+      <c r="D5" s="7">
+        <f t="shared" si="1"/>
+        <v>9.1160220994475141E-2</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A6" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="B6">
+        <v>367</v>
+      </c>
+      <c r="C6" s="7">
+        <f t="shared" si="0"/>
+        <v>1.4023155401016393E-2</v>
+      </c>
+      <c r="D6" s="7">
+        <f t="shared" si="1"/>
+        <v>2.2529158993247391E-2</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A7" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="B2">
+      <c r="B7">
         <v>9881</v>
       </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A3" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="B3">
-        <v>6577</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A4" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="B4">
-        <v>4322</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A5" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="B5">
-        <v>3539</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A6" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="B6">
-        <v>1485</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A7" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="B7">
-        <v>367</v>
+      <c r="C7" s="7">
+        <f t="shared" si="0"/>
+        <v>0.37755530931183373</v>
+      </c>
+      <c r="D7" s="7"/>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="B8">
+        <f>SUM(B2:B7)</f>
+        <v>26171</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="B9">
+        <f>SUM(B2:B6)</f>
+        <v>16290</v>
       </c>
     </row>
   </sheetData>
@@ -2551,7 +2975,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
-  <dimension ref="A1:G7"/>
+  <dimension ref="A1:G17"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="24.85546875" customWidth="1"/>
@@ -2724,6 +3148,89 @@
         <v>1850</v>
       </c>
     </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A11" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="B11" s="10" t="s">
+        <v>48</v>
+      </c>
+      <c r="C11" s="10" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A12" s="3">
+        <v>2019</v>
+      </c>
+      <c r="B12" s="11">
+        <v>408</v>
+      </c>
+      <c r="C12" s="12">
+        <f>B12/6576</f>
+        <v>6.2043795620437957E-2</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A13" s="3">
+        <v>2020</v>
+      </c>
+      <c r="B13" s="11">
+        <v>693</v>
+      </c>
+      <c r="C13" s="12">
+        <f t="shared" ref="C13:C17" si="0">B13/6576</f>
+        <v>0.10538321167883212</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A14" s="3">
+        <v>2021</v>
+      </c>
+      <c r="B14" s="11">
+        <v>1052</v>
+      </c>
+      <c r="C14" s="12">
+        <f t="shared" si="0"/>
+        <v>0.15997566909975669</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A15" s="3">
+        <v>2022</v>
+      </c>
+      <c r="B15" s="11">
+        <v>1471</v>
+      </c>
+      <c r="C15" s="12">
+        <f t="shared" si="0"/>
+        <v>0.22369221411192214</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A16" s="3">
+        <v>2023</v>
+      </c>
+      <c r="B16" s="11">
+        <v>1605</v>
+      </c>
+      <c r="C16" s="12">
+        <f t="shared" si="0"/>
+        <v>0.24406934306569342</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A17" s="3">
+        <v>2024</v>
+      </c>
+      <c r="B17" s="11">
+        <v>1347</v>
+      </c>
+      <c r="C17" s="12">
+        <f t="shared" si="0"/>
+        <v>0.20483576642335766</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
